--- a/amulet_controller/Generated/Testing/Testpoints/amulet_controller-testpoints.xlsx
+++ b/amulet_controller/Generated/Testing/Testpoints/amulet_controller-testpoints.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="370">
   <si>
     <t>Testpoint Ref.</t>
   </si>
@@ -71,7 +71,7 @@
     <t>MOTOR_ENABLE</t>
   </si>
   <si>
-    <t>TestPoint_Pad_D0.5mm_Front</t>
+    <t>TestPoint_Pad_D0.5mm</t>
   </si>
   <si>
     <t>TP2</t>
@@ -167,9 +167,6 @@
     <t>DRV_CS</t>
   </si>
   <si>
-    <t>TestPoint_Pad_D0.5mm_Back</t>
-  </si>
-  <si>
     <t>TP8</t>
   </si>
   <si>
@@ -857,7 +854,7 @@
     <t>GHA</t>
   </si>
   <si>
-    <t>TestPoint_Pad_D0.4mm_Front</t>
+    <t>TestPoint_Pad_D0.4mm</t>
   </si>
   <si>
     <t>TP60</t>
@@ -1576,12 +1573,12 @@
     <col min="6" max="6" width="14.7109375" customWidth="1"/>
     <col min="7" max="7" width="18.7109375" customWidth="1"/>
     <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="9" max="9" width="31.7109375" customWidth="1"/>
+    <col min="9" max="9" width="25.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="32" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1594,13 +1591,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>352</v>
-      </c>
       <c r="C2" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D2" s="3">
         <v>74</v>
@@ -1608,13 +1605,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>354</v>
-      </c>
       <c r="C3" s="2" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D3" s="3">
         <v>74</v>
@@ -1622,13 +1619,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>356</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D4" s="3">
         <v>74</v>
@@ -1636,13 +1633,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>358</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D5" s="3">
         <v>1</v>
@@ -1650,13 +1647,13 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>360</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D6" s="3">
         <v>74</v>
@@ -1891,33 +1888,33 @@
         <v>48</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="C16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="I16" s="8" t="s">
         <v>17</v>
@@ -1925,28 +1922,28 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="C17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="5" t="s">
+      <c r="E17" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="F17" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>58</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>59</v>
       </c>
       <c r="I17" s="5" t="s">
         <v>17</v>
@@ -1954,28 +1951,28 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="C18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="C18" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="8" t="s">
+      <c r="E18" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="8" t="s">
         <v>62</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>63</v>
       </c>
       <c r="I18" s="8" t="s">
         <v>17</v>
@@ -1983,28 +1980,28 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="C19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="5" t="s">
+      <c r="E19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="F19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="I19" s="5" t="s">
         <v>17</v>
@@ -2012,28 +2009,28 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B20" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="C20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C20" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="8" t="s">
+      <c r="E20" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E20" s="8" t="s">
+      <c r="F20" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>17</v>
@@ -2041,28 +2038,28 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="F21" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>78</v>
       </c>
       <c r="I21" s="5" t="s">
         <v>17</v>
@@ -2070,28 +2067,28 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="C22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="8" t="s">
+      <c r="E22" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E22" s="8" t="s">
+      <c r="F22" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="8" t="s">
         <v>82</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H22" s="8" t="s">
-        <v>83</v>
       </c>
       <c r="I22" s="8" t="s">
         <v>17</v>
@@ -2099,28 +2096,28 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="C23" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="F23" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>87</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="I23" s="5" t="s">
         <v>17</v>
@@ -2128,28 +2125,28 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="C24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E24" s="8" t="s">
+      <c r="F24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="8" t="s">
         <v>91</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G24" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="8" t="s">
-        <v>92</v>
       </c>
       <c r="I24" s="8" t="s">
         <v>17</v>
@@ -2157,28 +2154,28 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="F25" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="I25" s="5" t="s">
         <v>17</v>
@@ -2186,28 +2183,28 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="C26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="8" t="s">
+      <c r="E26" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="E26" s="8" t="s">
+      <c r="F26" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H26" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H26" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="I26" s="8" t="s">
         <v>17</v>
@@ -2215,28 +2212,28 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>17</v>
@@ -2244,28 +2241,28 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="C28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="C28" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D28" s="8" t="s">
+      <c r="E28" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="E28" s="8" t="s">
+      <c r="F28" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" s="8" t="s">
         <v>111</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H28" s="8" t="s">
-        <v>112</v>
       </c>
       <c r="I28" s="8" t="s">
         <v>17</v>
@@ -2273,28 +2270,28 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="B29" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="C29" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D29" s="5" t="s">
+      <c r="E29" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H29" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>17</v>
@@ -2302,28 +2299,28 @@
     </row>
     <row r="30" spans="1:9" ht="30" customHeight="1">
       <c r="A30" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="C30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C30" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D30" s="8" t="s">
+      <c r="E30" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E30" s="8" t="s">
+      <c r="F30" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H30" s="8" t="s">
         <v>121</v>
-      </c>
-      <c r="F30" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G30" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H30" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="I30" s="8" t="s">
         <v>17</v>
@@ -2331,19 +2328,19 @@
     </row>
     <row r="31" spans="1:9" ht="30" customHeight="1">
       <c r="A31" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="C31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C31" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>126</v>
       </c>
       <c r="F31" s="5" t="s">
         <v>47</v>
@@ -2352,36 +2349,36 @@
         <v>15</v>
       </c>
       <c r="H31" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="C32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C32" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D32" s="8" t="s">
+      <c r="E32" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="E32" s="8" t="s">
+      <c r="F32" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H32" s="8" t="s">
         <v>131</v>
-      </c>
-      <c r="F32" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H32" s="8" t="s">
-        <v>132</v>
       </c>
       <c r="I32" s="8" t="s">
         <v>17</v>
@@ -2389,28 +2386,28 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="C33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H33" s="5" t="s">
         <v>135</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>136</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>17</v>
@@ -2418,28 +2415,28 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>137</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="C34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="C34" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D34" s="8" t="s">
+      <c r="E34" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="F34" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="8" t="s">
         <v>139</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="F34" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G34" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="8" t="s">
-        <v>140</v>
       </c>
       <c r="I34" s="8" t="s">
         <v>17</v>
@@ -2447,28 +2444,28 @@
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B35" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="C35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="C35" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="5" t="s">
+      <c r="F35" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H35" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>144</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>17</v>
@@ -2476,28 +2473,28 @@
     </row>
     <row r="36" spans="1:9" ht="30" customHeight="1">
       <c r="A36" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="C36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="C36" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="8" t="s">
+      <c r="E36" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E36" s="8" t="s">
+      <c r="F36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H36" s="8" t="s">
         <v>148</v>
-      </c>
-      <c r="F36" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G36" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>149</v>
       </c>
       <c r="I36" s="8" t="s">
         <v>17</v>
@@ -2505,19 +2502,19 @@
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B37" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="C37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C37" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="E37" s="5" t="s">
         <v>152</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>153</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>47</v>
@@ -2526,27 +2523,27 @@
         <v>15</v>
       </c>
       <c r="H37" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B38" s="9" t="s">
+      <c r="C38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="C38" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="8" t="s">
+      <c r="E38" s="8" t="s">
         <v>157</v>
-      </c>
-      <c r="E38" s="8" t="s">
-        <v>158</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>47</v>
@@ -2555,36 +2552,36 @@
         <v>15</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="C39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H39" s="5" t="s">
         <v>163</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>164</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>17</v>
@@ -2592,28 +2589,28 @@
     </row>
     <row r="40" spans="1:9">
       <c r="A40" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="B40" s="9" t="s">
+      <c r="C40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H40" s="8" t="s">
         <v>166</v>
-      </c>
-      <c r="C40" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F40" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>167</v>
       </c>
       <c r="I40" s="8" t="s">
         <v>17</v>
@@ -2621,28 +2618,28 @@
     </row>
     <row r="41" spans="1:9">
       <c r="A41" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="C41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="5" t="s">
+      <c r="E41" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="F41" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H41" s="5" t="s">
         <v>171</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>172</v>
       </c>
       <c r="I41" s="5" t="s">
         <v>17</v>
@@ -2650,28 +2647,28 @@
     </row>
     <row r="42" spans="1:9">
       <c r="A42" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B42" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="C42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="C42" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D42" s="8" t="s">
+      <c r="E42" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="E42" s="8" t="s">
+      <c r="F42" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H42" s="8" t="s">
         <v>176</v>
-      </c>
-      <c r="F42" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G42" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>177</v>
       </c>
       <c r="I42" s="8" t="s">
         <v>17</v>
@@ -2679,19 +2676,19 @@
     </row>
     <row r="43" spans="1:9">
       <c r="A43" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="C43" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D43" s="5" t="s">
+      <c r="E43" s="5" t="s">
         <v>180</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>181</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>47</v>
@@ -2700,27 +2697,27 @@
         <v>15</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>183</v>
       </c>
-      <c r="B44" s="9" t="s">
+      <c r="C44" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="C44" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D44" s="8" t="s">
+      <c r="E44" s="8" t="s">
         <v>185</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>186</v>
       </c>
       <c r="F44" s="8" t="s">
         <v>47</v>
@@ -2729,36 +2726,36 @@
         <v>15</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="C45" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="C45" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D45" s="5" t="s">
+      <c r="E45" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="E45" s="5" t="s">
+      <c r="F45" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H45" s="5" t="s">
         <v>191</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H45" s="5" t="s">
-        <v>192</v>
       </c>
       <c r="I45" s="5" t="s">
         <v>17</v>
@@ -2766,28 +2763,28 @@
     </row>
     <row r="46" spans="1:9">
       <c r="A46" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="B46" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="B46" s="9" t="s">
+      <c r="C46" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="C46" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D46" s="8" t="s">
+      <c r="E46" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="E46" s="8" t="s">
+      <c r="F46" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H46" s="8" t="s">
         <v>196</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>197</v>
       </c>
       <c r="I46" s="8" t="s">
         <v>17</v>
@@ -2795,20 +2792,20 @@
     </row>
     <row r="47" spans="1:9">
       <c r="A47" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="C47" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="D47" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="E47" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="E47" s="5" t="s">
-        <v>202</v>
-      </c>
       <c r="F47" s="5" t="s">
         <v>14</v>
       </c>
@@ -2816,7 +2813,7 @@
         <v>15</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I47" s="5" t="s">
         <v>17</v>
@@ -2824,20 +2821,20 @@
     </row>
     <row r="48" spans="1:9">
       <c r="A48" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>198</v>
+      </c>
+      <c r="C48" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D48" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="B48" s="9" t="s">
-        <v>199</v>
-      </c>
-      <c r="C48" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="D48" s="8" t="s">
+      <c r="E48" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="E48" s="8" t="s">
-        <v>205</v>
-      </c>
       <c r="F48" s="8" t="s">
         <v>14</v>
       </c>
@@ -2845,7 +2842,7 @@
         <v>15</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I48" s="8" t="s">
         <v>17</v>
@@ -2853,20 +2850,20 @@
     </row>
     <row r="49" spans="1:9">
       <c r="A49" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D49" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D49" s="5" t="s">
+      <c r="E49" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="E49" s="5" t="s">
-        <v>208</v>
-      </c>
       <c r="F49" s="5" t="s">
         <v>14</v>
       </c>
@@ -2874,7 +2871,7 @@
         <v>15</v>
       </c>
       <c r="H49" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="I49" s="5" t="s">
         <v>17</v>
@@ -2882,28 +2879,28 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B50" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="B50" s="9" t="s">
+      <c r="C50" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="D50" s="8" t="s">
         <v>210</v>
       </c>
-      <c r="C50" s="9" t="s">
-        <v>200</v>
-      </c>
-      <c r="D50" s="8" t="s">
+      <c r="E50" s="8" t="s">
         <v>211</v>
       </c>
-      <c r="E50" s="8" t="s">
+      <c r="F50" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H50" s="8" t="s">
         <v>212</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>213</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>17</v>
@@ -2911,28 +2908,28 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>214</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="C51" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D51" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="C51" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D51" s="5" t="s">
+      <c r="E51" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E51" s="5" t="s">
+      <c r="F51" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H51" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H51" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="I51" s="5" t="s">
         <v>17</v>
@@ -2940,19 +2937,19 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>219</v>
       </c>
-      <c r="B52" s="9" t="s">
+      <c r="C52" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="C52" s="9" t="s">
+      <c r="D52" s="8" t="s">
         <v>221</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="E52" s="8" t="s">
         <v>222</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>223</v>
       </c>
       <c r="F52" s="8" t="s">
         <v>47</v>
@@ -2961,28 +2958,28 @@
         <v>15</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53" s="6" t="s">
         <v>225</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="C53" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="D53" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="E53" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="E53" s="5" t="s">
-        <v>229</v>
-      </c>
       <c r="F53" s="5" t="s">
         <v>14</v>
       </c>
@@ -2990,7 +2987,7 @@
         <v>15</v>
       </c>
       <c r="H53" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="I53" s="5" t="s">
         <v>17</v>
@@ -2998,20 +2995,20 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>230</v>
       </c>
-      <c r="B54" s="9" t="s">
+      <c r="C54" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="C54" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="D54" s="8" t="s">
+      <c r="E54" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>233</v>
-      </c>
       <c r="F54" s="8" t="s">
         <v>14</v>
       </c>
@@ -3019,7 +3016,7 @@
         <v>15</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I54" s="8" t="s">
         <v>17</v>
@@ -3027,19 +3024,19 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="D55" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B55" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>221</v>
-      </c>
-      <c r="D55" s="5" t="s">
+      <c r="E55" s="5" t="s">
         <v>235</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>47</v>
@@ -3048,28 +3045,28 @@
         <v>15</v>
       </c>
       <c r="H55" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="B56" s="9" t="s">
+      <c r="C56" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="C56" s="9" t="s">
+      <c r="D56" s="8" t="s">
         <v>239</v>
       </c>
-      <c r="D56" s="8" t="s">
+      <c r="E56" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>241</v>
-      </c>
       <c r="F56" s="8" t="s">
         <v>14</v>
       </c>
@@ -3077,7 +3074,7 @@
         <v>15</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I56" s="8" t="s">
         <v>17</v>
@@ -3085,20 +3082,20 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="D57" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="B57" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="D57" s="5" t="s">
+      <c r="E57" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="E57" s="5" t="s">
-        <v>244</v>
-      </c>
       <c r="F57" s="5" t="s">
         <v>14</v>
       </c>
@@ -3106,7 +3103,7 @@
         <v>15</v>
       </c>
       <c r="H57" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I57" s="5" t="s">
         <v>17</v>
@@ -3114,19 +3111,19 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>245</v>
       </c>
-      <c r="B58" s="9" t="s">
-        <v>238</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="D58" s="8" t="s">
+      <c r="E58" s="8" t="s">
         <v>246</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>247</v>
       </c>
       <c r="F58" s="8" t="s">
         <v>47</v>
@@ -3135,28 +3132,28 @@
         <v>15</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B59" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="C59" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="C59" s="6" t="s">
+      <c r="D59" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="E59" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="E59" s="5" t="s">
-        <v>252</v>
-      </c>
       <c r="F59" s="5" t="s">
         <v>14</v>
       </c>
@@ -3164,7 +3161,7 @@
         <v>15</v>
       </c>
       <c r="H59" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="I59" s="5" t="s">
         <v>17</v>
@@ -3172,20 +3169,20 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B60" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="C60" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D60" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="C60" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D60" s="8" t="s">
+      <c r="E60" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="E60" s="8" t="s">
-        <v>256</v>
-      </c>
       <c r="F60" s="8" t="s">
         <v>14</v>
       </c>
@@ -3193,7 +3190,7 @@
         <v>15</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I60" s="8" t="s">
         <v>17</v>
@@ -3201,20 +3198,20 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="5" t="s">
+        <v>256</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D61" s="5" t="s">
+      <c r="E61" s="5" t="s">
         <v>258</v>
       </c>
-      <c r="E61" s="5" t="s">
-        <v>259</v>
-      </c>
       <c r="F61" s="5" t="s">
         <v>14</v>
       </c>
@@ -3222,7 +3219,7 @@
         <v>15</v>
       </c>
       <c r="H61" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I61" s="5" t="s">
         <v>17</v>
@@ -3230,20 +3227,20 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D62" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="B62" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C62" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D62" s="8" t="s">
+      <c r="E62" s="8" t="s">
         <v>261</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>262</v>
-      </c>
       <c r="F62" s="8" t="s">
         <v>14</v>
       </c>
@@ -3251,7 +3248,7 @@
         <v>15</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I62" s="8" t="s">
         <v>17</v>
@@ -3259,20 +3256,20 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D63" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B63" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D63" s="5" t="s">
+      <c r="E63" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="E63" s="5" t="s">
-        <v>265</v>
-      </c>
       <c r="F63" s="5" t="s">
         <v>14</v>
       </c>
@@ -3280,7 +3277,7 @@
         <v>15</v>
       </c>
       <c r="H63" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>17</v>
@@ -3288,20 +3285,20 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D64" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="B64" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C64" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D64" s="8" t="s">
+      <c r="E64" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="E64" s="8" t="s">
-        <v>268</v>
-      </c>
       <c r="F64" s="8" t="s">
         <v>14</v>
       </c>
@@ -3309,7 +3306,7 @@
         <v>15</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I64" s="8" t="s">
         <v>17</v>
@@ -3317,20 +3314,20 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>269</v>
       </c>
-      <c r="B65" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>270</v>
-      </c>
       <c r="F65" s="5" t="s">
         <v>14</v>
       </c>
@@ -3338,7 +3335,7 @@
         <v>15</v>
       </c>
       <c r="H65" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I65" s="5" t="s">
         <v>17</v>
@@ -3346,19 +3343,19 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D66" s="8" t="s">
         <v>271</v>
       </c>
-      <c r="B66" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="C66" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D66" s="8" t="s">
+      <c r="E66" s="8" t="s">
         <v>272</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>273</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>47</v>
@@ -3367,297 +3364,297 @@
         <v>15</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I66" s="8" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="C67" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D67" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="C67" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D67" s="5" t="s">
+      <c r="E67" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="E67" s="5" t="s">
+      <c r="F67" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G67" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H67" s="5" t="s">
         <v>277</v>
       </c>
-      <c r="F67" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G67" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H67" s="5" t="s">
+      <c r="I67" s="5" t="s">
         <v>278</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B68" s="9" t="s">
         <v>280</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="C68" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E68" s="8" t="s">
         <v>281</v>
       </c>
-      <c r="C68" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="E68" s="8" t="s">
+      <c r="F68" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H68" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="F68" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H68" s="8" t="s">
-        <v>283</v>
-      </c>
       <c r="I68" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="B69" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="C69" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="C69" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D69" s="5" t="s">
+      <c r="E69" s="5" t="s">
         <v>286</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="F69" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H69" s="5" t="s">
         <v>287</v>
       </c>
-      <c r="F69" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G69" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H69" s="5" t="s">
-        <v>288</v>
-      </c>
       <c r="I69" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="B70" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="C70" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D70" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="C70" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D70" s="8" t="s">
+      <c r="E70" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="E70" s="8" t="s">
+      <c r="F70" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H70" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="F70" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H70" s="8" t="s">
-        <v>293</v>
-      </c>
       <c r="I70" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B71" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="C71" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D71" s="5" t="s">
         <v>295</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D71" s="5" t="s">
+      <c r="E71" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="E71" s="5" t="s">
+      <c r="F71" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H71" s="5" t="s">
         <v>297</v>
       </c>
-      <c r="F71" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H71" s="5" t="s">
-        <v>298</v>
-      </c>
       <c r="I71" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B72" s="9" t="s">
         <v>299</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="C72" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D72" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="C72" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D72" s="8" t="s">
+      <c r="E72" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="E72" s="8" t="s">
+      <c r="F72" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H72" s="8" t="s">
         <v>302</v>
       </c>
-      <c r="F72" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H72" s="8" t="s">
-        <v>303</v>
-      </c>
       <c r="I72" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="C73" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D73" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="C73" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D73" s="5" t="s">
+      <c r="E73" s="5" t="s">
         <v>306</v>
       </c>
-      <c r="E73" s="5" t="s">
+      <c r="F73" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H73" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="F73" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G73" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H73" s="5" t="s">
-        <v>308</v>
-      </c>
       <c r="I73" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="B74" s="9" t="s">
         <v>309</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="C74" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="E74" s="8" t="s">
         <v>310</v>
       </c>
-      <c r="C74" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="D74" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="E74" s="8" t="s">
+      <c r="F74" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H74" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="F74" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G74" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H74" s="8" t="s">
-        <v>312</v>
-      </c>
       <c r="I74" s="8" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="5" t="s">
+        <v>312</v>
+      </c>
+      <c r="B75" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="C75" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D75" s="5" t="s">
+      <c r="E75" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H75" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="E75" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="F75" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G75" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H75" s="5" t="s">
-        <v>316</v>
-      </c>
       <c r="I75" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B76" s="9" t="s">
         <v>317</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="C76" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="D76" s="8" t="s">
         <v>319</v>
       </c>
-      <c r="D76" s="8" t="s">
+      <c r="E76" s="8" t="s">
         <v>320</v>
       </c>
-      <c r="E76" s="8" t="s">
+      <c r="F76" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H76" s="8" t="s">
         <v>321</v>
-      </c>
-      <c r="F76" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H76" s="8" t="s">
-        <v>322</v>
       </c>
       <c r="I76" s="8" t="s">
         <v>17</v>
@@ -3665,28 +3662,28 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="C77" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D77" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="C77" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="D77" s="5" t="s">
+      <c r="E77" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H77" s="5" t="s">
         <v>325</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="F77" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G77" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H77" s="5" t="s">
-        <v>326</v>
       </c>
       <c r="I77" s="5" t="s">
         <v>17</v>
@@ -3694,28 +3691,28 @@
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="B78" s="9" t="s">
         <v>327</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="C78" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D78" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="C78" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="D78" s="8" t="s">
+      <c r="E78" s="8" t="s">
         <v>329</v>
       </c>
-      <c r="E78" s="8" t="s">
+      <c r="F78" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="8" t="s">
         <v>330</v>
-      </c>
-      <c r="F78" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H78" s="8" t="s">
-        <v>331</v>
       </c>
       <c r="I78" s="8" t="s">
         <v>17</v>
@@ -3723,28 +3720,28 @@
     </row>
     <row r="79" spans="1:9">
       <c r="A79" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="B79" s="6" t="s">
+      <c r="C79" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D79" s="5" t="s">
         <v>333</v>
       </c>
-      <c r="C79" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="D79" s="5" t="s">
+      <c r="E79" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H79" s="5" t="s">
         <v>334</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G79" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H79" s="5" t="s">
-        <v>335</v>
       </c>
       <c r="I79" s="5" t="s">
         <v>17</v>
@@ -3752,28 +3749,28 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="B80" s="9" t="s">
         <v>336</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="C80" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D80" s="8" t="s">
         <v>337</v>
       </c>
-      <c r="C80" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="D80" s="8" t="s">
+      <c r="E80" s="8" t="s">
         <v>338</v>
       </c>
-      <c r="E80" s="8" t="s">
+      <c r="F80" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H80" s="8" t="s">
         <v>339</v>
-      </c>
-      <c r="F80" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="H80" s="8" t="s">
-        <v>340</v>
       </c>
       <c r="I80" s="8" t="s">
         <v>17</v>
@@ -3781,28 +3778,28 @@
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>341</v>
       </c>
-      <c r="B81" s="6" t="s">
+      <c r="C81" s="6" t="s">
+        <v>318</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="C81" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="E81" s="5" t="s">
+      <c r="F81" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H81" s="5" t="s">
         <v>343</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G81" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="H81" s="5" t="s">
-        <v>344</v>
       </c>
       <c r="I81" s="5" t="s">
         <v>17</v>
@@ -3810,19 +3807,19 @@
     </row>
     <row r="82" spans="1:9">
       <c r="A82" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B82" s="9" t="s">
         <v>345</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="C82" s="9" t="s">
+        <v>253</v>
+      </c>
+      <c r="D82" s="8" t="s">
         <v>346</v>
       </c>
-      <c r="C82" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D82" s="8" t="s">
+      <c r="E82" s="8" t="s">
         <v>347</v>
-      </c>
-      <c r="E82" s="8" t="s">
-        <v>348</v>
       </c>
       <c r="F82" s="8" t="s">
         <v>47</v>
@@ -3831,10 +3828,10 @@
         <v>15</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I82" s="8" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3856,27 +3853,27 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="6" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="7" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/amulet_controller/Generated/Testing/Testpoints/amulet_controller-testpoints.xlsx
+++ b/amulet_controller/Generated/Testing/Testpoints/amulet_controller-testpoints.xlsx
@@ -1097,7 +1097,7 @@
     <t>KiCad Version:</t>
   </si>
   <si>
-    <t>8.0.5-8.0.5-0~ubuntu24.04.1</t>
+    <t>8.0.6-8.0.6-0~ubuntu24.04.1</t>
   </si>
   <si>
     <t>Component Groups:</t>
